--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118335259</v>
+        <v>118335265</v>
       </c>
       <c r="B3" t="n">
-        <v>90524</v>
+        <v>78484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388260</v>
+        <v>388245</v>
       </c>
       <c r="R3" t="n">
-        <v>6611587</v>
+        <v>6611592</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118335264</v>
+        <v>118335259</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>90524</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388238</v>
+        <v>388260</v>
       </c>
       <c r="R4" t="n">
-        <v>6611593</v>
+        <v>6611587</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118335262</v>
+        <v>118335266</v>
       </c>
       <c r="B6" t="n">
-        <v>90469</v>
+        <v>95394</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388207</v>
+        <v>388298</v>
       </c>
       <c r="R6" t="n">
-        <v>6611730</v>
+        <v>6611607</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118335266</v>
+        <v>118335262</v>
       </c>
       <c r="B7" t="n">
-        <v>95394</v>
+        <v>90469</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388298</v>
+        <v>388207</v>
       </c>
       <c r="R7" t="n">
-        <v>6611607</v>
+        <v>6611730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118335265</v>
+        <v>118335264</v>
       </c>
       <c r="B8" t="n">
         <v>78484</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388245</v>
+        <v>388238</v>
       </c>
       <c r="R8" t="n">
-        <v>6611592</v>
+        <v>6611593</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118746181</v>
+        <v>118746331</v>
       </c>
       <c r="B9" t="n">
-        <v>78740</v>
+        <v>90469</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6459</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388158</v>
+        <v>388205</v>
       </c>
       <c r="R9" t="n">
-        <v>6611698</v>
+        <v>6611728</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,26 +1490,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1526,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118746495</v>
+        <v>118746181</v>
       </c>
       <c r="B10" t="n">
-        <v>78485</v>
+        <v>78740</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>6459</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388231</v>
+        <v>388158</v>
       </c>
       <c r="R10" t="n">
-        <v>6611783</v>
+        <v>6611698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,11 +1584,6 @@
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammeltall</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1617,6 +1592,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1633,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118746331</v>
+        <v>118746017</v>
       </c>
       <c r="B11" t="n">
-        <v>90469</v>
+        <v>94513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1649,21 +1644,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1668,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388205</v>
+        <v>388127</v>
       </c>
       <c r="R11" t="n">
-        <v>6611728</v>
+        <v>6611713</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1862,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118746017</v>
+        <v>118746604</v>
       </c>
       <c r="B13" t="n">
-        <v>94513</v>
+        <v>57290</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1874,38 +1869,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388127</v>
+        <v>388249</v>
       </c>
       <c r="R13" t="n">
-        <v>6611713</v>
+        <v>6611737</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1938,6 +1938,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118746604</v>
+        <v>118746000</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>95394</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,39 +1985,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388249</v>
+        <v>388127</v>
       </c>
       <c r="R14" t="n">
-        <v>6611737</v>
+        <v>6611712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2045,11 +2045,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118746000</v>
+        <v>118746495</v>
       </c>
       <c r="B15" t="n">
-        <v>95394</v>
+        <v>78485</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,21 +2087,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>230405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388127</v>
+        <v>388231</v>
       </c>
       <c r="R15" t="n">
-        <v>6611712</v>
+        <v>6611783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2152,6 +2147,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammeltall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118335265</v>
+        <v>118335260</v>
       </c>
       <c r="B3" t="n">
         <v>78484</v>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388245</v>
+        <v>388150</v>
       </c>
       <c r="R3" t="n">
-        <v>6611592</v>
+        <v>6611703</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118335259</v>
+        <v>118335262</v>
       </c>
       <c r="B4" t="n">
-        <v>90524</v>
+        <v>90469</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388260</v>
+        <v>388207</v>
       </c>
       <c r="R4" t="n">
-        <v>6611587</v>
+        <v>6611730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118335260</v>
+        <v>118335266</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>95394</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388150</v>
+        <v>388298</v>
       </c>
       <c r="R5" t="n">
-        <v>6611703</v>
+        <v>6611607</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118335266</v>
+        <v>118335259</v>
       </c>
       <c r="B6" t="n">
-        <v>95394</v>
+        <v>90524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388298</v>
+        <v>388260</v>
       </c>
       <c r="R6" t="n">
-        <v>6611607</v>
+        <v>6611587</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118335262</v>
+        <v>118335264</v>
       </c>
       <c r="B7" t="n">
-        <v>90469</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,25 +1212,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388207</v>
+        <v>388238</v>
       </c>
       <c r="R7" t="n">
-        <v>6611730</v>
+        <v>6611593</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118335264</v>
+        <v>118335265</v>
       </c>
       <c r="B8" t="n">
         <v>78484</v>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388238</v>
+        <v>388245</v>
       </c>
       <c r="R8" t="n">
-        <v>6611593</v>
+        <v>6611592</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118746331</v>
+        <v>118746000</v>
       </c>
       <c r="B9" t="n">
-        <v>90469</v>
+        <v>95394</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388205</v>
+        <v>388127</v>
       </c>
       <c r="R9" t="n">
-        <v>6611728</v>
+        <v>6611712</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118746181</v>
+        <v>118746495</v>
       </c>
       <c r="B10" t="n">
-        <v>78740</v>
+        <v>78485</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6459</v>
+        <v>230405</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388158</v>
+        <v>388231</v>
       </c>
       <c r="R10" t="n">
-        <v>6611698</v>
+        <v>6611783</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,6 +1584,11 @@
           <t>2024-07-28</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammeltall</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1592,26 +1597,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1628,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118746017</v>
+        <v>118746331</v>
       </c>
       <c r="B11" t="n">
-        <v>94513</v>
+        <v>90469</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1644,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388127</v>
+        <v>388205</v>
       </c>
       <c r="R11" t="n">
-        <v>6611713</v>
+        <v>6611728</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118745853</v>
+        <v>118746017</v>
       </c>
       <c r="B12" t="n">
-        <v>5165</v>
+        <v>94513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,43 +1727,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102204</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388147</v>
+        <v>388127</v>
       </c>
       <c r="R12" t="n">
-        <v>6611748</v>
+        <v>6611713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1821,26 +1801,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Under bark på död ved</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Under bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1969,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118746000</v>
+        <v>118745853</v>
       </c>
       <c r="B14" t="n">
-        <v>95394</v>
+        <v>5165</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1985,34 +1945,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>102204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388127</v>
+        <v>388147</v>
       </c>
       <c r="R14" t="n">
-        <v>6611712</v>
+        <v>6611748</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,6 +2020,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Under bark på död ved</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Under bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2071,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118746495</v>
+        <v>118746181</v>
       </c>
       <c r="B15" t="n">
-        <v>78485</v>
+        <v>78740</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2083,25 +2068,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230405</v>
+        <v>6459</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388231</v>
+        <v>388158</v>
       </c>
       <c r="R15" t="n">
-        <v>6611783</v>
+        <v>6611698</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2149,11 +2134,6 @@
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Gammeltall</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2162,6 +2142,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>118335260</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118335262</v>
+        <v>118335259</v>
       </c>
       <c r="B4" t="n">
-        <v>90469</v>
+        <v>90531</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388207</v>
+        <v>388260</v>
       </c>
       <c r="R4" t="n">
-        <v>6611730</v>
+        <v>6611587</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118335266</v>
+        <v>118335264</v>
       </c>
       <c r="B5" t="n">
-        <v>95394</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388298</v>
+        <v>388238</v>
       </c>
       <c r="R5" t="n">
-        <v>6611607</v>
+        <v>6611593</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118335259</v>
+        <v>118335262</v>
       </c>
       <c r="B6" t="n">
-        <v>90524</v>
+        <v>90476</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,25 +1110,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388260</v>
+        <v>388207</v>
       </c>
       <c r="R6" t="n">
-        <v>6611587</v>
+        <v>6611730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118335264</v>
+        <v>118335266</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>95401</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388238</v>
+        <v>388298</v>
       </c>
       <c r="R7" t="n">
-        <v>6611593</v>
+        <v>6611607</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
         <v>118335265</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>118746000</v>
       </c>
       <c r="B9" t="n">
-        <v>95394</v>
+        <v>95401</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118746495</v>
+        <v>118746017</v>
       </c>
       <c r="B10" t="n">
-        <v>78485</v>
+        <v>94520</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>230405</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388231</v>
+        <v>388127</v>
       </c>
       <c r="R10" t="n">
-        <v>6611783</v>
+        <v>6611713</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-07-28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammeltall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118746331</v>
+        <v>118746181</v>
       </c>
       <c r="B11" t="n">
-        <v>90469</v>
+        <v>78747</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388205</v>
+        <v>388158</v>
       </c>
       <c r="R11" t="n">
-        <v>6611728</v>
+        <v>6611698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1694,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1715,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118746017</v>
+        <v>118746331</v>
       </c>
       <c r="B12" t="n">
-        <v>94513</v>
+        <v>90476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>388127</v>
+        <v>388205</v>
       </c>
       <c r="R12" t="n">
-        <v>6611713</v>
+        <v>6611728</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118746604</v>
+        <v>118745853</v>
       </c>
       <c r="B13" t="n">
-        <v>57290</v>
+        <v>5165</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,27 +1848,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1862,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388249</v>
+        <v>388147</v>
       </c>
       <c r="R13" t="n">
-        <v>6611737</v>
+        <v>6611748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,11 +1915,6 @@
           <t>2024-07-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gamla ringhack i tall.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1913,6 +1923,26 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Under bark på död ved</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Under bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1929,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118745853</v>
+        <v>118746604</v>
       </c>
       <c r="B14" t="n">
-        <v>5165</v>
+        <v>57290</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,27 +1975,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102204</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1974,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388147</v>
+        <v>388249</v>
       </c>
       <c r="R14" t="n">
-        <v>6611748</v>
+        <v>6611737</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,6 +2042,11 @@
           <t>2024-07-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gamla ringhack i tall.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2020,26 +2055,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Under bark på död ved</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Under bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2056,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118746181</v>
+        <v>118746495</v>
       </c>
       <c r="B15" t="n">
-        <v>78740</v>
+        <v>78492</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2068,25 +2083,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6459</v>
+        <v>230405</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2096,10 +2111,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388158</v>
+        <v>388231</v>
       </c>
       <c r="R15" t="n">
-        <v>6611698</v>
+        <v>6611783</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,6 +2149,11 @@
           <t>2024-07-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammeltall</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2142,26 +2162,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -1404,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118746000</v>
+        <v>118746181</v>
       </c>
       <c r="B9" t="n">
-        <v>95401</v>
+        <v>78747</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6459</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388127</v>
+        <v>388158</v>
       </c>
       <c r="R9" t="n">
-        <v>6611712</v>
+        <v>6611698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1490,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1506,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118746017</v>
+        <v>118745853</v>
       </c>
       <c r="B10" t="n">
-        <v>94520</v>
+        <v>5165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,38 +1538,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>102204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388127</v>
+        <v>388147</v>
       </c>
       <c r="R10" t="n">
-        <v>6611713</v>
+        <v>6611748</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1617,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Under bark på död ved</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Under bark of dead wood # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1608,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118746181</v>
+        <v>118746000</v>
       </c>
       <c r="B11" t="n">
-        <v>78747</v>
+        <v>95401</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1665,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>388158</v>
+        <v>388127</v>
       </c>
       <c r="R11" t="n">
-        <v>6611698</v>
+        <v>6611712</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,26 +1739,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1832,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118745853</v>
+        <v>118746017</v>
       </c>
       <c r="B13" t="n">
-        <v>5165</v>
+        <v>94520</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,43 +1869,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102204</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>388147</v>
+        <v>388127</v>
       </c>
       <c r="R13" t="n">
-        <v>6611748</v>
+        <v>6611713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1923,26 +1943,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Under bark på död ved</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Under bark of dead wood # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1959,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118746604</v>
+        <v>118746495</v>
       </c>
       <c r="B14" t="n">
-        <v>57290</v>
+        <v>78492</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1975,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>388249</v>
+        <v>388231</v>
       </c>
       <c r="R14" t="n">
-        <v>6611737</v>
+        <v>6611783</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Gamla ringhack i tall.</t>
+          <t>Gammeltall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,10 +2066,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118746495</v>
+        <v>118746604</v>
       </c>
       <c r="B15" t="n">
-        <v>78492</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,34 +2082,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>388231</v>
+        <v>388249</v>
       </c>
       <c r="R15" t="n">
-        <v>6611783</v>
+        <v>6611737</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gammeltall</t>
+          <t>Gamla ringhack i tall.</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2176,6 +2176,441 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123697832</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>388187</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6611666</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123697981</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>388279</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6611643</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123698366</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>388233</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6611534</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123698235</v>
+      </c>
+      <c r="B19" t="n">
+        <v>90986</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>388276</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6611645</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123697832</v>
+        <v>123697981</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388187</v>
+        <v>388279</v>
       </c>
       <c r="R16" t="n">
-        <v>6611666</v>
+        <v>6611643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123697981</v>
+        <v>123698235</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>91003</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,47 +2301,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388279</v>
+        <v>388276</v>
       </c>
       <c r="R17" t="n">
-        <v>6611643</v>
+        <v>6611645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123698366</v>
+        <v>123697832</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2435,7 +2426,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2445,14 +2436,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388233</v>
+        <v>388187</v>
       </c>
       <c r="R18" t="n">
-        <v>6611534</v>
+        <v>6611666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123698235</v>
+        <v>123698366</v>
       </c>
       <c r="B19" t="n">
-        <v>90986</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,38 +2514,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388276</v>
+        <v>388233</v>
       </c>
       <c r="R19" t="n">
-        <v>6611645</v>
+        <v>6611534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123697981</v>
+        <v>123698235</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,47 +2190,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388279</v>
+        <v>388276</v>
       </c>
       <c r="R16" t="n">
-        <v>6611643</v>
+        <v>6611645</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,10 +2280,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123698235</v>
+        <v>123698366</v>
       </c>
       <c r="B17" t="n">
-        <v>91003</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,38 +2292,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388276</v>
+        <v>388233</v>
       </c>
       <c r="R17" t="n">
-        <v>6611645</v>
+        <v>6611534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2391,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123697832</v>
+        <v>123697981</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388187</v>
+        <v>388279</v>
       </c>
       <c r="R18" t="n">
-        <v>6611666</v>
+        <v>6611643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123698366</v>
+        <v>123697832</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2547,14 +2547,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388233</v>
+        <v>388187</v>
       </c>
       <c r="R19" t="n">
-        <v>6611534</v>
+        <v>6611666</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123698235</v>
+        <v>123697832</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,38 +2190,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388276</v>
+        <v>388187</v>
       </c>
       <c r="R16" t="n">
-        <v>6611645</v>
+        <v>6611666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123698366</v>
+        <v>123698235</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>91010</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2292,47 +2301,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388233</v>
+        <v>388276</v>
       </c>
       <c r="R17" t="n">
-        <v>6611534</v>
+        <v>6611645</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2394,7 +2394,7 @@
         <v>123697981</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123697832</v>
+        <v>123698366</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2547,14 +2547,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388187</v>
+        <v>388233</v>
       </c>
       <c r="R19" t="n">
-        <v>6611666</v>
+        <v>6611534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2181,7 +2181,7 @@
         <v>123697832</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123698235</v>
+        <v>123697981</v>
       </c>
       <c r="B17" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,38 +2301,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388276</v>
+        <v>388279</v>
       </c>
       <c r="R17" t="n">
-        <v>6611645</v>
+        <v>6611643</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123697981</v>
+        <v>123698235</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>91010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2403,47 +2412,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388279</v>
+        <v>388276</v>
       </c>
       <c r="R18" t="n">
-        <v>6611643</v>
+        <v>6611645</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2505,7 +2505,7 @@
         <v>123698366</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2178,7 +2178,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123697832</v>
+        <v>123697981</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388187</v>
+        <v>388279</v>
       </c>
       <c r="R16" t="n">
-        <v>6611666</v>
+        <v>6611643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123697981</v>
+        <v>123697832</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388279</v>
+        <v>388187</v>
       </c>
       <c r="R17" t="n">
-        <v>6611643</v>
+        <v>6611666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123698235</v>
+        <v>123698366</v>
       </c>
       <c r="B18" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,38 +2412,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388276</v>
+        <v>388233</v>
       </c>
       <c r="R18" t="n">
-        <v>6611645</v>
+        <v>6611534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123698366</v>
+        <v>123698235</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,47 +2523,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388233</v>
+        <v>388276</v>
       </c>
       <c r="R19" t="n">
-        <v>6611534</v>
+        <v>6611645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123697981</v>
+        <v>123698235</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,47 +2190,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388279</v>
+        <v>388276</v>
       </c>
       <c r="R16" t="n">
-        <v>6611643</v>
+        <v>6611645</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2289,7 +2280,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123697832</v>
+        <v>123698366</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2324,7 +2315,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2334,14 +2325,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388187</v>
+        <v>388233</v>
       </c>
       <c r="R17" t="n">
-        <v>6611666</v>
+        <v>6611534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2400,7 +2391,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123698366</v>
+        <v>123697832</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2435,7 +2426,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2445,14 +2436,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388233</v>
+        <v>388187</v>
       </c>
       <c r="R18" t="n">
-        <v>6611534</v>
+        <v>6611666</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2511,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123698235</v>
+        <v>123697981</v>
       </c>
       <c r="B19" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,38 +2514,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388276</v>
+        <v>388279</v>
       </c>
       <c r="R19" t="n">
-        <v>6611645</v>
+        <v>6611643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2178,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123698235</v>
+        <v>123698366</v>
       </c>
       <c r="B16" t="n">
-        <v>91010</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2190,38 +2190,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>388276</v>
+        <v>388233</v>
       </c>
       <c r="R16" t="n">
-        <v>6611645</v>
+        <v>6611534</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2280,7 +2289,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123698366</v>
+        <v>123697832</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2315,7 +2324,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2325,14 +2334,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skogsbergstjärnet, Skogsbergstjärnet, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388233</v>
+        <v>388187</v>
       </c>
       <c r="R17" t="n">
-        <v>6611534</v>
+        <v>6611666</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2391,7 +2400,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123697832</v>
+        <v>123697981</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2426,7 +2435,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2440,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>388187</v>
+        <v>388279</v>
       </c>
       <c r="R18" t="n">
-        <v>6611666</v>
+        <v>6611643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2502,10 +2511,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123697981</v>
+        <v>123698235</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>91010</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,47 +2523,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>388279</v>
+        <v>388276</v>
       </c>
       <c r="R19" t="n">
-        <v>6611643</v>
+        <v>6611645</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2611,6 +2611,657 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125684869</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>53</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>388303</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6611585</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125684874</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>388250</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6611670</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125684871</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91186</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>388261</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6611590</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125684873</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92448</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>388247</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6611608</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125684870</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>388242</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6611608</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-08-19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125684768</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>388197</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6611680</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2613,15 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125684869</v>
+        <v>125684870</v>
       </c>
       <c r="B20" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2629,21 +2624,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2648,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>388303</v>
+        <v>388242</v>
       </c>
       <c r="R20" t="n">
-        <v>6611585</v>
+        <v>6611608</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2683,12 +2678,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2720,15 +2715,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125684874</v>
+        <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91240</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2736,39 +2726,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>388250</v>
+        <v>388261</v>
       </c>
       <c r="R21" t="n">
-        <v>6611670</v>
+        <v>6611590</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2832,50 +2817,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125684871</v>
+        <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>388261</v>
+        <v>388197</v>
       </c>
       <c r="R22" t="n">
-        <v>6611590</v>
+        <v>6611680</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2902,12 +2886,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2939,37 +2923,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125684873</v>
+        <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>92448</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2979,10 +2958,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>388247</v>
+        <v>388303</v>
       </c>
       <c r="R23" t="n">
-        <v>6611608</v>
+        <v>6611585</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3009,12 +2988,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3046,15 +3025,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125684870</v>
+        <v>125684874</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3062,34 +3036,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>388242</v>
+        <v>388250</v>
       </c>
       <c r="R24" t="n">
-        <v>6611608</v>
+        <v>6611670</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3153,54 +3132,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125684768</v>
+        <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>388197</v>
+        <v>388247</v>
       </c>
       <c r="R25" t="n">
-        <v>6611680</v>
+        <v>6611608</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3227,12 +3197,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3261,6 +3231,500 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>125850458</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>388234</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6611675</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>125850822</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91234</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>388213</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6611723</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>125850341</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>388242</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6611602</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>125852849</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78634</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>353</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>388267</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6611648</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>125852876</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91170</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>112</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>388265</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6611648</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2718,7 +2718,7 @@
         <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91234</v>
+        <v>91241</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91170</v>
+        <v>91177</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91241</v>
+        <v>91242</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>125852849</v>
       </c>
       <c r="B29" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91177</v>
+        <v>91178</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2616,7 +2616,7 @@
         <v>125684870</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>92509</v>
+        <v>92518</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2616,7 +2616,7 @@
         <v>125684870</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>92518</v>
+        <v>92522</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91242</v>
+        <v>91246</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>125852849</v>
       </c>
       <c r="B29" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91178</v>
+        <v>91182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2616,7 +2616,7 @@
         <v>125684870</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>125684874</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>125852849</v>
       </c>
       <c r="B29" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91182</v>
+        <v>91184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2718,7 +2718,7 @@
         <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91184</v>
+        <v>91186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2718,7 +2718,7 @@
         <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91186</v>
+        <v>91188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2616,7 +2616,7 @@
         <v>125684870</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>125684871</v>
       </c>
       <c r="B21" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>125684874</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>125684873</v>
       </c>
       <c r="B25" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>125852849</v>
       </c>
       <c r="B29" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91188</v>
+        <v>91192</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -2820,7 +2820,7 @@
         <v>125684768</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>125684869</v>
       </c>
       <c r="B23" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 21243-2024 artfynd.xlsx
+++ b/artfynd/A 21243-2024 artfynd.xlsx
@@ -3237,7 +3237,7 @@
         <v>125850458</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>125850822</v>
       </c>
       <c r="B27" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
         <v>125850341</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>125852849</v>
       </c>
       <c r="B29" t="n">
-        <v>78644</v>
+        <v>78647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3634,7 +3634,7 @@
         <v>125852876</v>
       </c>
       <c r="B30" t="n">
-        <v>91192</v>
+        <v>91195</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
